--- a/mistral_translate_work/split_by_prompt/excel/phantom_skill/lang_phantom/lang_phantom__phantom_skill__part_0002.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/phantom_skill/lang_phantom/lang_phantom__phantom_skill__part_0002.xlsx
@@ -578,7 +578,7 @@
         <is>
           <t>Biến hình thành Excarat, lặn xuống đất và di chuyển về phía trước. Trong trạng thái lặn, có thể thay đổi hướng di chuyển và không chịu sát thương.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
         <is>
           <t>Biến hình thành Excarat, lặn xuống đất và di chuyển về phía trước. Trong trạng thái lặn, có thể thay đổi hướng di chuyển và không chịu sát thương.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
         <is>
           <t>Biến hình thành Excarat, lặn xuống đất và di chuyển về phía trước. Trong trạng thái lặn, có thể thay đổi hướng di chuyển và không chịu sát thương.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -785,7 +785,7 @@
         <is>
           <t>Biến hình thành Excarat, lặn xuống đất và di chuyển về phía trước. Trong trạng thái lặn, có thể thay đổi hướng di chuyển và không chịu sát thương.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
         <is>
           <t>Biến hình thành Excarat, lặn xuống đất và di chuyển về phía trước. Trong trạng thái lặn, có thể thay đổi hướng di chuyển và không chịu sát thương.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -923,7 +923,7 @@
         <is>
           <t>Biến hình thành Excarat, lặn xuống đất và di chuyển về phía trước. Trong trạng thái lặn, có thể thay đổi hướng di chuyển và không chịu sát thương.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -992,7 +992,7 @@
         <is>
           <t>Biến hình thành Excarat, lặn xuống đất và di chuyển về phía trước. Trong trạng thái lặn, có thể thay đổi hướng di chuyển và không chịu sát thương.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
         <is>
           <t>Biến hình thành Excarat, lặn xuống đất và di chuyển về phía trước. Trong trạng thái lặn, có thể thay đổi hướng di chuyển và không chịu sát thương.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
         <is>
           <t>Biến hình thành Excarat, lặn xuống đất và di chuyển về phía trước. Trong trạng thái lặn, có thể thay đổi hướng di chuyển và không chịu sát thương.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
         <is>
           <t>Biến hình thành Excarat, lặn xuống đất và di chuyển về phía trước. Trong trạng thái lặn, có thể thay đổi hướng di chuyển và không chịu sát thương.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
         <is>
           <t>Biến hình thành Excarat, lặn xuống đất và di chuyển về phía trước. Trong trạng thái lặn, có thể thay đổi hướng di chuyển và không chịu sát thương.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
         <is>
           <t>Biến hình thành Excarat, lặn xuống đất và di chuyển về phía trước. Trong trạng thái lặn, có thể thay đổi hướng di chuyển và không chịu sát thương.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
         <is>
           <t>Biến hình thành Excarat, lặn xuống đất và di chuyển về phía trước. Trong trạng thái lặn, có thể thay đổi hướng di chuyển và không chịu sát thương.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
         <is>
           <t>Biến hình thành Excarat, lặn xuống đất và di chuyển về phía trước. Trong trạng thái lặn, có thể thay đổi hướng di chuyển và không chịu sát thương.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
         <is>
           <t>Biến hình thành Excarat, lặn xuống đất và di chuyển về phía trước. Trong trạng thái lặn, có thể thay đổi hướng di chuyển và không chịu sát thương.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
         <is>
           <t>Biến hình thành Excarat, lặn xuống đất và di chuyển về phía trước. Trong trạng thái lặn, có thể thay đổi hướng di chuyển và không chịu sát thương.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
         <is>
           <t>Biến hình thành Excarat, lặn xuống đất và di chuyển về phía trước. Trong trạng thái lặn, có thể thay đổi hướng di chuyển và không chịu sát thương.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
         <is>
           <t>Biến hình thành Excarat, lặn xuống đất và di chuyển về phía trước. Trong trạng thái lặn, có thể thay đổi hướng di chuyển và không chịu sát thương.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
         <is>
           <t>Biến hình thành Excarat, lặn xuống đất và di chuyển về phía trước. Trong trạng thái lặn, có thể thay đổi hướng di chuyển và không chịu sát thương.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -1889,7 +1889,7 @@
         <is>
           <t>Biến hình thành Excarat, lặn xuống đất và di chuyển về phía trước. Trong trạng thái lặn, có thể thay đổi hướng di chuyển và không chịu sát thương.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1958,7 @@
         <is>
           <t>Summon Geohide Saurian non để đập mạnh kẻ địch phía trước, gây {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2027,7 @@
         <is>
           <t>Summon Geohide Saurian non để đập mạnh kẻ địch phía trước, gây {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
         <is>
           <t>Summon Geohide Saurian non để đập mạnh kẻ địch phía trước, gây {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
         <is>
           <t>Summon Geohide Saurian non để đập mạnh kẻ địch phía trước, gây {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
         <is>
           <t>Summon Geohide Saurian non để đập mạnh kẻ địch phía trước, gây {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -2303,7 +2303,7 @@
         <is>
           <t>Summon Geohide Saurian non để đập mạnh kẻ địch phía trước, gây {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -2372,7 +2372,7 @@
         <is>
           <t>Summon Geohide Saurian non để đập mạnh kẻ địch phía trước, gây {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
         <is>
           <t>Summon Geohide Saurian non để đập mạnh kẻ địch phía trước, gây {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -2510,7 +2510,7 @@
         <is>
           <t>Summon Geohide Saurian non để đập mạnh kẻ địch phía trước, gây {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -2579,7 +2579,7 @@
         <is>
           <t>Summon Geohide Saurian non để đập mạnh kẻ địch phía trước, gây {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
         <is>
           <t>Summon Geohide Saurian non để đập mạnh kẻ địch phía trước, gây {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -2717,7 +2717,7 @@
         <is>
           <t>Summon Geohide Saurian non để đập mạnh kẻ địch phía trước, gây {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -2786,7 +2786,7 @@
         <is>
           <t>Summon Geohide Saurian non để đập mạnh kẻ địch phía trước, gây {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
         <is>
           <t>Summon Geohide Saurian non để đập mạnh kẻ địch phía trước, gây {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
         <is>
           <t>Summon Geohide Saurian non để đập mạnh kẻ địch phía trước, gây {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -2993,7 +2993,7 @@
         <is>
           <t>Summon Geohide Saurian non để đập mạnh kẻ địch phía trước, gây {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -3062,7 +3062,7 @@
         <is>
           <t>Summon Geohide Saurian non để đập mạnh kẻ địch phía trước, gây {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3131,7 @@
         <is>
           <t>Summon Geohide Saurian non để đập mạnh kẻ địch phía trước, gây {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -3200,7 +3200,7 @@
         <is>
           <t>Summon Geohide Saurian non để đập mạnh kẻ địch phía trước, gây {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -3269,7 +3269,7 @@
         <is>
           <t>Summon Geohide Saurian non để đập mạnh kẻ địch phía trước, gây {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -3338,7 +3338,7 @@
         <is>
           <t>Summon Geohide Saurian trưởng thành để phun hơi, mỗi lần gây {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -3407,7 +3407,7 @@
         <is>
           <t>Summon Geohide Saurian trưởng thành để phun hơi, mỗi lần gây {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
         <is>
           <t>Summon Geohide Saurian trưởng thành để phun hơi, mỗi lần gây {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3545,7 @@
         <is>
           <t>Summon Geohide Saurian trưởng thành để phun hơi, mỗi lần gây {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -3614,7 +3614,7 @@
         <is>
           <t>Summon Geohide Saurian trưởng thành để phun hơi, mỗi lần gây {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3683,7 @@
         <is>
           <t>Summon Geohide Saurian trưởng thành để phun hơi, mỗi lần gây {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -3752,7 +3752,7 @@
         <is>
           <t>Summon Geohide Saurian trưởng thành để phun hơi, mỗi lần gây {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
         <is>
           <t>Summon Geohide Saurian trưởng thành để phun hơi, mỗi lần gây {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3890,7 @@
         <is>
           <t>Summon Geohide Saurian trưởng thành để phun hơi, mỗi lần gây {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -3959,7 +3959,7 @@
         <is>
           <t>Summon Geohide Saurian trưởng thành để phun hơi, mỗi lần gây {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -4028,7 +4028,7 @@
         <is>
           <t>Summon Geohide Saurian trưởng thành để phun hơi, mỗi lần gây {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -4097,7 +4097,7 @@
         <is>
           <t>Summon Geohide Saurian trưởng thành để phun hơi, mỗi lần gây {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4166,7 @@
         <is>
           <t>Summon Geohide Saurian trưởng thành để phun hơi, mỗi lần gây {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
         <is>
           <t>Summon Geohide Saurian trưởng thành để phun hơi, mỗi lần gây {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -4304,7 +4304,7 @@
         <is>
           <t>Summon Geohide Saurian trưởng thành để phun hơi, mỗi lần gây {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -4373,7 +4373,7 @@
         <is>
           <t>Summon Geohide Saurian trưởng thành để phun hơi, mỗi lần gây {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
         <is>
           <t>Summon Geohide Saurian trưởng thành để phun hơi, mỗi lần gây {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -4511,7 +4511,7 @@
         <is>
           <t>Summon Geohide Saurian trưởng thành để phun hơi, mỗi lần gây {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
         <is>
           <t>Summon Geohide Saurian trưởng thành để phun hơi, mỗi lần gây {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -4649,7 +4649,7 @@
         <is>
           <t>Summon Geohide Saurian trưởng thành để phun hơi, mỗi lần gây {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
         <is>
           <t>Summon Roseshroom trưởng thành để hất tung kẻ địch gần đó, gây {0}% Havoc DMG và thổi bay chúng lên không.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -4787,7 +4787,7 @@
         <is>
           <t>Summon Roseshroom trưởng thành để hất tung kẻ địch gần đó, gây {0}% Havoc DMG và thổi bay chúng lên không.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4856,7 @@
         <is>
           <t>Summon Roseshroom trưởng thành để hất tung kẻ địch gần đó, gây {0}% Havoc DMG và thổi bay chúng lên không.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4925,7 @@
         <is>
           <t>Summon Roseshroom trưởng thành để hất tung kẻ địch gần đó, gây {0}% Havoc DMG và thổi bay chúng lên không.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
         <is>
           <t>Summon Roseshroom trưởng thành để hất tung kẻ địch gần đó, gây {0}% Havoc DMG và thổi bay chúng lên không.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
         <is>
           <t>Summon Roseshroom trưởng thành để hất tung kẻ địch gần đó, gây {0}% Havoc DMG và thổi bay chúng lên không.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -5132,7 +5132,7 @@
         <is>
           <t>Summon Roseshroom trưởng thành để hất tung kẻ địch gần đó, gây {0}% Havoc DMG và thổi bay chúng lên không.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
         <is>
           <t>Summon Roseshroom trưởng thành để hất tung kẻ địch gần đó, gây {0}% Havoc DMG và thổi bay chúng lên không.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
         <is>
           <t>Summon Roseshroom trưởng thành để hất tung kẻ địch gần đó, gây {0}% Havoc DMG và thổi bay chúng lên không.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -5339,7 +5339,7 @@
         <is>
           <t>Summon Roseshroom trưởng thành để hất tung kẻ địch gần đó, gây {0}% Havoc DMG và thổi bay chúng lên không.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -5408,7 +5408,7 @@
         <is>
           <t>Summon Roseshroom trưởng thành để hất tung kẻ địch gần đó, gây {0}% Havoc DMG và thổi bay chúng lên không.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -5477,7 +5477,7 @@
         <is>
           <t>Summon Roseshroom trưởng thành để hất tung kẻ địch gần đó, gây {0}% Havoc DMG và thổi bay chúng lên không.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -5546,7 +5546,7 @@
         <is>
           <t>Summon Roseshroom trưởng thành để hất tung kẻ địch gần đó, gây {0}% Havoc DMG và thổi bay chúng lên không.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -5615,7 +5615,7 @@
         <is>
           <t>Summon Roseshroom trưởng thành để hất tung kẻ địch gần đó, gây {0}% Havoc DMG và thổi bay chúng lên không.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -5684,7 +5684,7 @@
         <is>
           <t>Summon Roseshroom trưởng thành để hất tung kẻ địch gần đó, gây {0}% Havoc DMG và thổi bay chúng lên không.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -5753,7 +5753,7 @@
         <is>
           <t>Summon Roseshroom trưởng thành để hất tung kẻ địch gần đó, gây {0}% Havoc DMG và thổi bay chúng lên không.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -5822,7 +5822,7 @@
         <is>
           <t>Summon Roseshroom trưởng thành để hất tung kẻ địch gần đó, gây {0}% Havoc DMG và thổi bay chúng lên không.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -5891,7 +5891,7 @@
         <is>
           <t>Summon Roseshroom trưởng thành để hất tung kẻ địch gần đó, gây {0}% Havoc DMG và thổi bay chúng lên không.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
         <is>
           <t>Summon Roseshroom trưởng thành để hất tung kẻ địch gần đó, gây {0}% Havoc DMG và thổi bay chúng lên không.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -6029,7 +6029,7 @@
         <is>
           <t>Summon Roseshroom trưởng thành để hất tung kẻ địch gần đó, gây {0}% Havoc DMG và thổi bay chúng lên không.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -6098,7 +6098,7 @@
         <is>
           <t>Summon Frostbite Tertoise để tấn công xung quanh, gây {0}% Glacio DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -6167,7 +6167,7 @@
         <is>
           <t>Summon Frostbite Tertoise để tấn công xung quanh, gây {0}% Glacio DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
         <is>
           <t>Summon Frostbite Tertoise để tấn công xung quanh, gây {0}% Glacio DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -6305,7 +6305,7 @@
         <is>
           <t>Summon Frostbite Tertoise để tấn công xung quanh, gây {0}% Glacio DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -6374,7 +6374,7 @@
         <is>
           <t>Summon Frostbite Tertoise để tấn công xung quanh, gây {0}% Glacio DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -6443,7 +6443,7 @@
         <is>
           <t>Summon Frostbite Tertoise để tấn công xung quanh, gây {0}% Glacio DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -6512,7 +6512,7 @@
         <is>
           <t>Summon Frostbite Tertoise để tấn công xung quanh, gây {0}% Glacio DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -6581,7 +6581,7 @@
         <is>
           <t>Summon Frostbite Tertoise để tấn công xung quanh, gây {0}% Glacio DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
         <is>
           <t>Summon Frostbite Tertoise để tấn công xung quanh, gây {0}% Glacio DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -6719,7 +6719,7 @@
         <is>
           <t>Summon Frostbite Tertoise để tấn công xung quanh, gây {0}% Glacio DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6788,7 @@
         <is>
           <t>Summon Frostbite Tertoise để tấn công xung quanh, gây {0}% Glacio DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -6857,7 +6857,7 @@
         <is>
           <t>Summon Frostbite Tertoise để tấn công xung quanh, gây {0}% Glacio DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -6926,7 +6926,7 @@
         <is>
           <t>Summon Frostbite Tertoise để tấn công xung quanh, gây {0}% Glacio DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -6995,7 +6995,7 @@
         <is>
           <t>Summon Frostbite Tertoise để tấn công xung quanh, gây {0}% Glacio DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -7064,7 +7064,7 @@
         <is>
           <t>Summon Frostbite Tertoise để tấn công xung quanh, gây {0}% Glacio DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -7133,7 +7133,7 @@
         <is>
           <t>Summon Frostbite Tertoise để tấn công xung quanh, gây {0}% Glacio DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -7202,7 +7202,7 @@
         <is>
           <t>Summon Frostbite Tertoise để tấn công xung quanh, gây {0}% Glacio DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -7271,7 +7271,7 @@
         <is>
           <t>Summon Frostbite Tertoise để tấn công xung quanh, gây {0}% Glacio DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -7340,7 +7340,7 @@
         <is>
           <t>Summon Frostbite Tertoise để tấn công xung quanh, gây {0}% Glacio DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -7409,7 +7409,7 @@
         <is>
           <t>Summon Frostbite Tertoise để tấn công xung quanh, gây {0}% Glacio DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
         <is>
           <t>Biến hình thành Spearback Ursa và lao về phía trước, gây sát thương cho kẻ địch trên đường đi. Mỗi lần va chạm gây {0}% Physical DMG. Thời gian biến hình có thể duy trì tối đa {1} giây.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
         <is>
           <t>Biến hình thành Spearback Ursa và lao về phía trước, gây sát thương cho kẻ địch trên đường đi. Mỗi lần va chạm gây {0}% Physical DMG. Thời gian biến hình có thể duy trì tối đa {1} giây.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -7616,7 +7616,7 @@
         <is>
           <t>Biến hình thành Spearback Ursa và lao về phía trước, gây sát thương cho kẻ địch trên đường đi. Mỗi lần va chạm gây {0}% Physical DMG. Thời gian biến hình có thể duy trì tối đa {1} giây.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -7685,7 +7685,7 @@
         <is>
           <t>Biến hình thành Spearback Ursa và lao về phía trước, gây sát thương cho kẻ địch trên đường đi. Mỗi lần va chạm gây {0}% Physical DMG. Thời gian biến hình có thể duy trì tối đa {1} giây.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7754,7 @@
         <is>
           <t>Biến hình thành Spearback Ursa và lao về phía trước, gây sát thương cho kẻ địch trên đường đi. Mỗi lần va chạm gây {0}% Physical DMG. Thời gian biến hình có thể duy trì tối đa {1} giây.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -7823,7 +7823,7 @@
         <is>
           <t>Biến hình thành Spearback Ursa và lao về phía trước, gây sát thương cho kẻ địch trên đường đi. Mỗi lần va chạm gây {0}% Physical DMG. Thời gian biến hình có thể duy trì tối đa {1} giây.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -7892,7 +7892,7 @@
         <is>
           <t>Biến hình thành Spearback Ursa và lao về phía trước, gây sát thương cho kẻ địch trên đường đi. Mỗi lần va chạm gây {0}% Physical DMG. Thời gian biến hình có thể duy trì tối đa {1} giây.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
         <is>
           <t>Biến hình thành Spearback Ursa và lao về phía trước, gây sát thương cho kẻ địch trên đường đi. Mỗi lần va chạm gây {0}% Physical DMG. Thời gian biến hình có thể duy trì tối đa {1} giây.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -8030,7 +8030,7 @@
         <is>
           <t>Biến hình thành Spearback Ursa và lao về phía trước, gây sát thương cho kẻ địch trên đường đi. Mỗi lần va chạm gây {0}% Physical DMG. Thời gian biến hình có thể duy trì tối đa {1} giây.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -8099,7 +8099,7 @@
         <is>
           <t>Biến hình thành Spearback Ursa và lao về phía trước, gây sát thương cho kẻ địch trên đường đi. Mỗi lần va chạm gây {0}% Physical DMG. Thời gian biến hình có thể duy trì tối đa {1} giây.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
         <is>
           <t>Biến hình thành Spearback Ursa và lao về phía trước, gây sát thương cho kẻ địch trên đường đi. Mỗi lần va chạm gây {0}% Physical DMG. Thời gian biến hình có thể duy trì tối đa {1} giây.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8237,7 @@
         <is>
           <t>Biến hình thành Spearback Ursa và lao về phía trước, gây sát thương cho kẻ địch trên đường đi. Mỗi lần va chạm gây {0}% Physical DMG. Thời gian biến hình có thể duy trì tối đa {1} giây.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -8306,7 +8306,7 @@
         <is>
           <t>Biến hình thành Spearback Ursa và lao về phía trước, gây sát thương cho kẻ địch trên đường đi. Mỗi lần va chạm gây {0}% Physical DMG. Thời gian biến hình có thể duy trì tối đa {1} giây.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -8375,7 +8375,7 @@
         <is>
           <t>Biến hình thành Spearback Ursa và lao về phía trước, gây sát thương cho kẻ địch trên đường đi. Mỗi lần va chạm gây {0}% Physical DMG. Thời gian biến hình có thể duy trì tối đa {1} giây.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -8444,7 +8444,7 @@
         <is>
           <t>Biến hình thành Spearback Ursa và lao về phía trước, gây sát thương cho kẻ địch trên đường đi. Mỗi lần va chạm gây {0}% Physical DMG. Thời gian biến hình có thể duy trì tối đa {1} giây.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -8513,7 +8513,7 @@
         <is>
           <t>Biến hình thành Spearback Ursa và lao về phía trước, gây sát thương cho kẻ địch trên đường đi. Mỗi lần va chạm gây {0}% Physical DMG. Thời gian biến hình có thể duy trì tối đa {1} giây.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -8582,7 +8582,7 @@
         <is>
           <t>Biến hình thành Spearback Ursa và lao về phía trước, gây sát thương cho kẻ địch trên đường đi. Mỗi lần va chạm gây {0}% Physical DMG. Thời gian biến hình có thể duy trì tối đa {1} giây.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -8651,7 +8651,7 @@
         <is>
           <t>Biến hình thành Spearback Ursa và lao về phía trước, gây sát thương cho kẻ địch trên đường đi. Mỗi lần va chạm gây {0}% Physical DMG. Thời gian biến hình có thể duy trì tối đa {1} giây.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -8720,7 +8720,7 @@
         <is>
           <t>Biến hình thành Spearback Ursa và lao về phía trước, gây sát thương cho kẻ địch trên đường đi. Mỗi lần va chạm gây {0}% Physical DMG. Thời gian biến hình có thể duy trì tối đa {1} giây.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -8789,7 +8789,7 @@
         <is>
           <t>Biến hình thành Spearback Ursa và lao về phía trước, gây sát thương cho kẻ địch trên đường đi. Mỗi lần va chạm gây {0}% Physical DMG. Thời gian biến hình có thể duy trì tối đa {1} giây.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -8858,7 +8858,7 @@
         <is>
           <t>Biến hình thành Shadow Dreadmane và quất đuôi, gây {0}% Havoc DMG, đồng thời tạo ra một lưỡi kiếm năng lượng ở phía trước gây {1}% Havoc DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -8927,7 +8927,7 @@
         <is>
           <t>Biến hình thành Shadow Dreadmane và quất đuôi, gây {0}% Havoc DMG, đồng thời tạo ra một lưỡi kiếm năng lượng ở phía trước gây {1}% Havoc DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -8996,7 +8996,7 @@
         <is>
           <t>Biến hình thành Shadow Dreadmane và quất đuôi, gây {0}% Havoc DMG, đồng thời tạo ra một lưỡi kiếm năng lượng ở phía trước gây {1}% Havoc DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -9065,7 +9065,7 @@
         <is>
           <t>Biến hình thành Shadow Dreadmane và quất đuôi, gây {0}% Havoc DMG, đồng thời tạo ra một lưỡi kiếm năng lượng ở phía trước gây {1}% Havoc DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
         <is>
           <t>Biến hình thành Shadow Dreadmane và quất đuôi, gây {0}% Havoc DMG, đồng thời tạo ra một lưỡi kiếm năng lượng ở phía trước gây {1}% Havoc DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -9203,7 +9203,7 @@
         <is>
           <t>Biến hình thành Shadow Dreadmane và quất đuôi, gây {0}% Havoc DMG, đồng thời tạo ra một lưỡi kiếm năng lượng ở phía trước gây {1}% Havoc DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -9272,7 +9272,7 @@
         <is>
           <t>Biến hình thành Shadow Dreadmane và quất đuôi, gây {0}% Havoc DMG, đồng thời tạo ra một lưỡi kiếm năng lượng ở phía trước gây {1}% Havoc DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -9341,7 +9341,7 @@
         <is>
           <t>Biến hình thành Shadow Dreadmane và quất đuôi, gây {0}% Havoc DMG, đồng thời tạo ra một lưỡi kiếm năng lượng ở phía trước gây {1}% Havoc DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -9410,7 +9410,7 @@
         <is>
           <t>Biến hình thành Shadow Dreadmane và quất đuôi, gây {0}% Havoc DMG, đồng thời tạo ra một lưỡi kiếm năng lượng ở phía trước gây {1}% Havoc DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -9479,7 +9479,7 @@
         <is>
           <t>Biến hình thành Shadow Dreadmane và quất đuôi, gây {0}% Havoc DMG, đồng thời tạo ra một lưỡi kiếm năng lượng ở phía trước gây {1}% Havoc DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -9548,7 +9548,7 @@
         <is>
           <t>Biến hình thành Shadow Dreadmane và quất đuôi, gây {0}% Havoc DMG, đồng thời tạo ra một lưỡi kiếm năng lượng ở phía trước gây {1}% Havoc DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
         <is>
           <t>Biến hình thành Shadow Dreadmane và quất đuôi, gây {0}% Havoc DMG, đồng thời tạo ra một lưỡi kiếm năng lượng ở phía trước gây {1}% Havoc DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -9686,7 +9686,7 @@
         <is>
           <t>Biến hình thành Shadow Dreadmane và quất đuôi, gây {0}% Havoc DMG, đồng thời tạo ra một lưỡi kiếm năng lượng ở phía trước gây {1}% Havoc DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -9755,7 +9755,7 @@
         <is>
           <t>Biến hình thành Shadow Dreadmane và quất đuôi, gây {0}% Havoc DMG, đồng thời tạo ra một lưỡi kiếm năng lượng ở phía trước gây {1}% Havoc DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -9824,7 +9824,7 @@
         <is>
           <t>Biến hình thành Shadow Dreadmane và quất đuôi, gây {0}% Havoc DMG, đồng thời tạo ra một lưỡi kiếm năng lượng ở phía trước gây {1}% Havoc DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -9893,7 +9893,7 @@
         <is>
           <t>Biến hình thành Shadow Dreadmane và quất đuôi, gây {0}% Havoc DMG, đồng thời tạo ra một lưỡi kiếm năng lượng ở phía trước gây {1}% Havoc DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -9962,7 +9962,7 @@
         <is>
           <t>Biến hình thành Shadow Dreadmane và quất đuôi, gây {0}% Havoc DMG, đồng thời tạo ra một lưỡi kiếm năng lượng ở phía trước gây {1}% Havoc DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -10031,7 +10031,7 @@
         <is>
           <t>Biến hình thành Shadow Dreadmane và quất đuôi, gây {0}% Havoc DMG, đồng thời tạo ra một lưỡi kiếm năng lượng ở phía trước gây {1}% Havoc DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -10100,7 +10100,7 @@
         <is>
           <t>Biến hình thành Shadow Dreadmane và quất đuôi, gây {0}% Havoc DMG, đồng thời tạo ra một lưỡi kiếm năng lượng ở phía trước gây {1}% Havoc DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -10169,7 +10169,7 @@
         <is>
           <t>Biến hình thành Shadow Dreadmane và quất đuôi, gây {0}% Havoc DMG, đồng thời tạo ra một lưỡi kiếm năng lượng ở phía trước gây {1}% Havoc DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -10238,7 +10238,7 @@
         <is>
           <t>Summon Fusion Dreadmane và quất đuôi gây {0}% Fusion DMG, đồng thời tạo thành 3 quả cầu năng lượng, mỗi quả gây {1}% Fusion DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -10307,7 +10307,7 @@
         <is>
           <t>Summon Fusion Dreadmane và quất đuôi gây {0}% Fusion DMG, đồng thời tạo thành 3 quả cầu năng lượng, mỗi quả gây {1}% Fusion DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -10376,7 +10376,7 @@
         <is>
           <t>Summon Fusion Dreadmane và quất đuôi gây {0}% Fusion DMG, đồng thời tạo thành 3 quả cầu năng lượng, mỗi quả gây {1}% Fusion DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -10445,7 +10445,7 @@
         <is>
           <t>Summon Fusion Dreadmane và quất đuôi gây {0}% Fusion DMG, đồng thời tạo thành 3 quả cầu năng lượng, mỗi quả gây {1}% Fusion DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -10514,7 +10514,7 @@
         <is>
           <t>Summon Fusion Dreadmane và quất đuôi gây {0}% Fusion DMG, đồng thời tạo thành 3 quả cầu năng lượng, mỗi quả gây {1}% Fusion DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -10583,7 +10583,7 @@
         <is>
           <t>Summon Fusion Dreadmane và quất đuôi gây {0}% Fusion DMG, đồng thời tạo thành 3 quả cầu năng lượng, mỗi quả gây {1}% Fusion DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -10652,7 +10652,7 @@
         <is>
           <t>Summon Fusion Dreadmane và quất đuôi gây {0}% Fusion DMG, đồng thời tạo thành 3 quả cầu năng lượng, mỗi quả gây {1}% Fusion DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -10721,7 +10721,7 @@
         <is>
           <t>Summon Fusion Dreadmane và quất đuôi gây {0}% Fusion DMG, đồng thời tạo thành 3 quả cầu năng lượng, mỗi quả gây {1}% Fusion DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -10790,7 +10790,7 @@
         <is>
           <t>Summon Fusion Dreadmane và quất đuôi gây {0}% Fusion DMG, đồng thời tạo thành 3 quả cầu năng lượng, mỗi quả gây {1}% Fusion DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -10859,7 +10859,7 @@
         <is>
           <t>Summon Fusion Dreadmane và quất đuôi gây {0}% Fusion DMG, đồng thời tạo thành 3 quả cầu năng lượng, mỗi quả gây {1}% Fusion DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -10928,7 +10928,7 @@
         <is>
           <t>Summon Fusion Dreadmane và quất đuôi gây {0}% Fusion DMG, đồng thời tạo thành 3 quả cầu năng lượng, mỗi quả gây {1}% Fusion DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -10997,7 +10997,7 @@
         <is>
           <t>Summon Fusion Dreadmane và quất đuôi gây {0}% Fusion DMG, đồng thời tạo thành 3 quả cầu năng lượng, mỗi quả gây {1}% Fusion DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -11066,7 +11066,7 @@
         <is>
           <t>Summon Fusion Dreadmane và quất đuôi gây {0}% Fusion DMG, đồng thời tạo thành 3 quả cầu năng lượng, mỗi quả gây {1}% Fusion DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -11135,7 +11135,7 @@
         <is>
           <t>Summon Fusion Dreadmane và quất đuôi gây {0}% Fusion DMG, đồng thời tạo thành 3 quả cầu năng lượng, mỗi quả gây {1}% Fusion DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -11204,7 +11204,7 @@
         <is>
           <t>Summon Fusion Dreadmane và quất đuôi gây {0}% Fusion DMG, đồng thời tạo thành 3 quả cầu năng lượng, mỗi quả gây {1}% Fusion DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -11273,7 +11273,7 @@
         <is>
           <t>Summon Fusion Dreadmane và quất đuôi gây {0}% Fusion DMG, đồng thời tạo thành 3 quả cầu năng lượng, mỗi quả gây {1}% Fusion DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -11342,7 +11342,7 @@
         <is>
           <t>Summon Fusion Dreadmane và quất đuôi gây {0}% Fusion DMG, đồng thời tạo thành 3 quả cầu năng lượng, mỗi quả gây {1}% Fusion DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -11411,7 +11411,7 @@
         <is>
           <t>Summon Fusion Dreadmane và quất đuôi gây {0}% Fusion DMG, đồng thời tạo thành 3 quả cầu năng lượng, mỗi quả gây {1}% Fusion DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -11480,7 +11480,7 @@
         <is>
           <t>Summon Fusion Dreadmane và quất đuôi gây {0}% Fusion DMG, đồng thời tạo thành 3 quả cầu năng lượng, mỗi quả gây {1}% Fusion DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -11549,7 +11549,7 @@
         <is>
           <t>Summon Fusion Dreadmane và quất đuôi gây {0}% Fusion DMG, đồng thời tạo thành 3 quả cầu năng lượng, mỗi quả gây {1}% Fusion DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -11618,7 +11618,7 @@
         <is>
           <t>Biến hình thành Thunder Squama và phóng về phía trước, mỗi giai đoạn gây {0}% Electro DMG, sau đó tung đòn kết thúc gây {1}% Electro DMG. Các tia sét sẽ gây {2}% Electro DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -11687,7 +11687,7 @@
         <is>
           <t>Biến hình thành Thunder Squama và phóng về phía trước, mỗi giai đoạn gây {0}% Electro DMG, sau đó tung đòn kết thúc gây {1}% Electro DMG. Các tia sét sẽ gây {2}% Electro DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -11756,7 +11756,7 @@
         <is>
           <t>Biến hình thành Thunder Squama và phóng về phía trước, mỗi giai đoạn gây {0}% Electro DMG, sau đó tung đòn kết thúc gây {1}% Electro DMG. Các tia sét sẽ gây {2}% Electro DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -11825,7 +11825,7 @@
         <is>
           <t>Biến hình thành Thunder Squama và phóng về phía trước, mỗi giai đoạn gây {0}% Electro DMG, sau đó tung đòn kết thúc gây {1}% Electro DMG. Các tia sét sẽ gây {2}% Electro DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -11894,7 +11894,7 @@
         <is>
           <t>Biến hình thành Thunder Squama và phóng về phía trước, mỗi giai đoạn gây {0}% Electro DMG, sau đó tung đòn kết thúc gây {1}% Electro DMG. Các tia sét sẽ gây {2}% Electro DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -11963,7 +11963,7 @@
         <is>
           <t>Biến hình thành Thunder Squama và phóng về phía trước, mỗi giai đoạn gây {0}% Electro DMG, sau đó tung đòn kết thúc gây {1}% Electro DMG. Các tia sét sẽ gây {2}% Electro DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -12032,7 +12032,7 @@
         <is>
           <t>Biến hình thành Thunder Squama và phóng về phía trước, mỗi giai đoạn gây {0}% Electro DMG, sau đó tung đòn kết thúc gây {1}% Electro DMG. Các tia sét sẽ gây {2}% Electro DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -12101,7 +12101,7 @@
         <is>
           <t>Biến hình thành Thunder Squama và phóng về phía trước, mỗi giai đoạn gây {0}% Electro DMG, sau đó tung đòn kết thúc gây {1}% Electro DMG. Các tia sét sẽ gây {2}% Electro DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -12170,7 +12170,7 @@
         <is>
           <t>Biến hình thành Thunder Squama và phóng về phía trước, mỗi giai đoạn gây {0}% Electro DMG, sau đó tung đòn kết thúc gây {1}% Electro DMG. Các tia sét sẽ gây {2}% Electro DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -12239,7 +12239,7 @@
         <is>
           <t>Biến hình thành Thunder Squama và phóng về phía trước, mỗi giai đoạn gây {0}% Electro DMG, sau đó tung đòn kết thúc gây {1}% Electro DMG. Các tia sét sẽ gây {2}% Electro DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -12308,7 +12308,7 @@
         <is>
           <t>Biến hình thành Thunder Squama và phóng về phía trước, mỗi giai đoạn gây {0}% Electro DMG, sau đó tung đòn kết thúc gây {1}% Electro DMG. Các tia sét sẽ gây {2}% Electro DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -12377,7 +12377,7 @@
         <is>
           <t>Biến hình thành Thunder Squama và phóng về phía trước, mỗi giai đoạn gây {0}% Electro DMG, sau đó tung đòn kết thúc gây {1}% Electro DMG. Các tia sét sẽ gây {2}% Electro DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -12446,7 +12446,7 @@
         <is>
           <t>Biến hình thành Thunder Squama và phóng về phía trước, mỗi giai đoạn gây {0}% Electro DMG, sau đó tung đòn kết thúc gây {1}% Electro DMG. Các tia sét sẽ gây {2}% Electro DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -12515,7 +12515,7 @@
         <is>
           <t>Biến hình thành Thunder Squama và phóng về phía trước, mỗi giai đoạn gây {0}% Electro DMG, sau đó tung đòn kết thúc gây {1}% Electro DMG. Các tia sét sẽ gây {2}% Electro DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -12584,7 +12584,7 @@
         <is>
           <t>Biến hình thành Thunder Squama và phóng về phía trước, mỗi giai đoạn gây {0}% Electro DMG, sau đó tung đòn kết thúc gây {1}% Electro DMG. Các tia sét sẽ gây {2}% Electro DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -12653,7 +12653,7 @@
         <is>
           <t>Biến hình thành Thunder Squama và phóng về phía trước, mỗi giai đoạn gây {0}% Electro DMG, sau đó tung đòn kết thúc gây {1}% Electro DMG. Các tia sét sẽ gây {2}% Electro DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -12722,7 +12722,7 @@
         <is>
           <t>Biến hình thành Thunder Squama và phóng về phía trước, mỗi giai đoạn gây {0}% Electro DMG, sau đó tung đòn kết thúc gây {1}% Electro DMG. Các tia sét sẽ gây {2}% Electro DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -12791,7 +12791,7 @@
         <is>
           <t>Biến hình thành Thunder Squama và phóng về phía trước, mỗi giai đoạn gây {0}% Electro DMG, sau đó tung đòn kết thúc gây {1}% Electro DMG. Các tia sét sẽ gây {2}% Electro DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -12860,7 +12860,7 @@
         <is>
           <t>Biến hình thành Thunder Squama và phóng về phía trước, mỗi giai đoạn gây {0}% Electro DMG, sau đó tung đòn kết thúc gây {1}% Electro DMG. Các tia sét sẽ gây {2}% Electro DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -12929,7 +12929,7 @@
         <is>
           <t>Biến hình thành Thunder Squama và phóng về phía trước, mỗi giai đoạn gây {0}% Electro DMG, sau đó tung đòn kết thúc gây {1}% Electro DMG. Các tia sét sẽ gây {2}% Electro DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -12998,7 +12998,7 @@
         <is>
           <t>Biến hình thành Inferno Rider và tung ra một đòn đánh, gây {0}% Fusion DMG. Giữ nút kỹ năng để tung thêm một đòn nữa, gây {1}% Fusion DMG. Sau đó kích hoạt vụ nổ, gây {2}% Fusion DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -13067,7 +13067,7 @@
         <is>
           <t>Biến hình thành Inferno Rider và tung ra một đòn đánh, gây {0}% Fusion DMG. Giữ nút kỹ năng để tung thêm một đòn nữa, gây {1}% Fusion DMG. Sau đó kích hoạt vụ nổ, gây {2}% Fusion DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -13136,7 +13136,7 @@
         <is>
           <t>Biến hình thành Inferno Rider và tung ra một đòn đánh, gây {0}% Fusion DMG. Giữ nút kỹ năng để tung thêm một đòn nữa, gây {1}% Fusion DMG. Sau đó kích hoạt vụ nổ, gây {2}% Fusion DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -13205,7 +13205,7 @@
         <is>
           <t>Biến hình thành Inferno Rider và tung ra một đòn đánh, gây {0}% Fusion DMG. Giữ nút kỹ năng để tung thêm một đòn nữa, gây {1}% Fusion DMG. Sau đó kích hoạt vụ nổ, gây {2}% Fusion DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -13274,7 +13274,7 @@
         <is>
           <t>Biến hình thành Inferno Rider và tung ra một đòn đánh, gây {0}% Fusion DMG. Giữ nút kỹ năng để tung thêm một đòn nữa, gây {1}% Fusion DMG. Sau đó kích hoạt vụ nổ, gây {2}% Fusion DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -13343,7 +13343,7 @@
         <is>
           <t>Biến hình thành Inferno Rider và tung ra một đòn đánh, gây {0}% Fusion DMG. Giữ nút kỹ năng để tung thêm một đòn nữa, gây {1}% Fusion DMG. Sau đó kích hoạt vụ nổ, gây {2}% Fusion DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -13412,7 +13412,7 @@
         <is>
           <t>Biến hình thành Inferno Rider và tung ra một đòn đánh, gây {0}% Fusion DMG. Giữ nút kỹ năng để tung thêm một đòn nữa, gây {1}% Fusion DMG. Sau đó kích hoạt vụ nổ, gây {2}% Fusion DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -13481,7 +13481,7 @@
         <is>
           <t>Biến hình thành Inferno Rider và tung ra một đòn đánh, gây {0}% Fusion DMG. Giữ nút kỹ năng để tung thêm một đòn nữa, gây {1}% Fusion DMG. Sau đó kích hoạt vụ nổ, gây {2}% Fusion DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -13550,7 +13550,7 @@
         <is>
           <t>Biến hình thành Inferno Rider và tung ra một đòn đánh, gây {0}% Fusion DMG. Giữ nút kỹ năng để tung thêm một đòn nữa, gây {1}% Fusion DMG. Sau đó kích hoạt vụ nổ, gây {2}% Fusion DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -13619,7 +13619,7 @@
         <is>
           <t>Biến hình thành Inferno Rider và tung ra một đòn đánh, gây {0}% Fusion DMG. Giữ nút kỹ năng để tung thêm một đòn nữa, gây {1}% Fusion DMG. Sau đó kích hoạt vụ nổ, gây {2}% Fusion DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -13688,7 +13688,7 @@
         <is>
           <t>Biến hình thành Inferno Rider và tung ra một đòn đánh, gây {0}% Fusion DMG. Giữ nút kỹ năng để tung thêm một đòn nữa, gây {1}% Fusion DMG. Sau đó kích hoạt vụ nổ, gây {2}% Fusion DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -13757,7 +13757,7 @@
         <is>
           <t>Biến hình thành Inferno Rider và tung ra một đòn đánh, gây {0}% Fusion DMG. Giữ nút kỹ năng để tung thêm một đòn nữa, gây {1}% Fusion DMG. Sau đó kích hoạt vụ nổ, gây {2}% Fusion DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -13826,7 +13826,7 @@
         <is>
           <t>Biến hình thành Inferno Rider và tung ra một đòn đánh, gây {0}% Fusion DMG. Giữ nút kỹ năng để tung thêm một đòn nữa, gây {1}% Fusion DMG. Sau đó kích hoạt vụ nổ, gây {2}% Fusion DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -13895,7 +13895,7 @@
         <is>
           <t>Biến hình thành Inferno Rider và tung ra một đòn đánh, gây {0}% Fusion DMG. Giữ nút kỹ năng để tung thêm một đòn nữa, gây {1}% Fusion DMG. Sau đó kích hoạt vụ nổ, gây {2}% Fusion DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -13964,7 +13964,7 @@
         <is>
           <t>Biến hình thành Inferno Rider và tung ra một đòn đánh, gây {0}% Fusion DMG. Giữ nút kỹ năng để tung thêm một đòn nữa, gây {1}% Fusion DMG. Sau đó kích hoạt vụ nổ, gây {2}% Fusion DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -14033,7 +14033,7 @@
         <is>
           <t>Biến hình thành Inferno Rider và tung ra một đòn đánh, gây {0}% Fusion DMG. Giữ nút kỹ năng để tung thêm một đòn nữa, gây {1}% Fusion DMG. Sau đó kích hoạt vụ nổ, gây {2}% Fusion DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -14102,7 +14102,7 @@
         <is>
           <t>Biến hình thành Inferno Rider và tung ra một đòn đánh, gây {0}% Fusion DMG. Giữ nút kỹ năng để tung thêm một đòn nữa, gây {1}% Fusion DMG. Sau đó kích hoạt vụ nổ, gây {2}% Fusion DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -14171,7 +14171,7 @@
         <is>
           <t>Biến hình thành Inferno Rider và tung ra một đòn đánh, gây {0}% Fusion DMG. Giữ nút kỹ năng để tung thêm một đòn nữa, gây {1}% Fusion DMG. Sau đó kích hoạt vụ nổ, gây {2}% Fusion DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -14240,7 +14240,7 @@
         <is>
           <t>Biến hình thành Inferno Rider và tung ra một đòn đánh, gây {0}% Fusion DMG. Giữ nút kỹ năng để tung thêm một đòn nữa, gây {1}% Fusion DMG. Sau đó kích hoạt vụ nổ, gây {2}% Fusion DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -14309,7 +14309,7 @@
         <is>
           <t>Biến hình thành Inferno Rider và tung ra một đòn đánh, gây {0}% Fusion DMG. Giữ nút kỹ năng để tung thêm một đòn nữa, gây {1}% Fusion DMG. Sau đó kích hoạt vụ nổ, gây {2}% Fusion DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
